--- a/demo_gui_mail_hang_loat_dinh_kem_rieng.xlsx
+++ b/demo_gui_mail_hang_loat_dinh_kem_rieng.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\00.Demo\66.Demo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\00.Demo\67demoguiemail\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{887FB6DC-BCA8-4BD7-8808-3C4B29BA8CB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
@@ -17,7 +17,6 @@
     <sheet name="huong_dan_demo" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
